--- a/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt1_rubricas.xlsx
@@ -1968,13 +1968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9455E6B1-8A7D-4EFA-8C81-563E7688C9E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82D8C2F8-6215-47E8-A42E-C9A95F6F4852}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F7104F3-322E-4E88-B230-AC4FF4570941}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBAD5F74-DF01-4141-992D-E9E0444C8668}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14FD1595-FCD4-42EE-9040-7C4C6AC81534}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D1A6600-92E7-4946-ABA1-C31BB8CB0343}"/>
 </file>